--- a/artfynd/A 12737-2025 artfynd.xlsx
+++ b/artfynd/A 12737-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103998580</v>
+        <v>103998696</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Åhöjdens sluttning, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554587.2590248903</v>
+        <v>554711</v>
       </c>
       <c r="R2" t="n">
-        <v>7017618.192240465</v>
+        <v>7017223</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,50 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103998674</v>
+        <v>103998580</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åhöjdens sluttning, Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554479.5126017473</v>
+        <v>554587</v>
       </c>
       <c r="R3" t="n">
-        <v>7017353.962924789</v>
+        <v>7017618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,37 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103998592</v>
+        <v>103998702</v>
       </c>
       <c r="B4" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554634.4377847618</v>
+        <v>554695</v>
       </c>
       <c r="R4" t="n">
-        <v>7017600.090015956</v>
+        <v>7017674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,6 +998,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1041,12 +1031,7 @@
         <v>103998584</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554677.7239647229</v>
+        <v>554678</v>
       </c>
       <c r="R5" t="n">
-        <v>7017174.575715548</v>
+        <v>7017174</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1162,12 +1147,7 @@
         <v>103998635</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554625.2233065373</v>
+        <v>554625</v>
       </c>
       <c r="R6" t="n">
-        <v>7017134.071865291</v>
+        <v>7017134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,6 +1253,238 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103998674</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åhöjdens sluttning, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>554479</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7017354</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103998592</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stenbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>554634</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7017600</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
